--- a/ZonasEscolares/excels/ANCASH-CARHUAZ-CARHUAZ.xlsx
+++ b/ZonasEscolares/excels/ANCASH-CARHUAZ-CARHUAZ.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/ANCASH-CARHUAZ-CARHUAZ.xlsx
+++ b/ZonasEscolares/excels/ANCASH-CARHUAZ-CARHUAZ.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>070</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-9.279640000000001</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.645572</v>
-      </c>
-      <c r="I2" t="n">
-        <v>358</v>
-      </c>
-      <c r="J2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-9.27964</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.645572</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>86314 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-9.284394000000001</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.59685</v>
-      </c>
-      <c r="I3" t="n">
-        <v>220</v>
-      </c>
-      <c r="J3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-9.284394</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.59685</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>86269 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-9.278441000000001</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.647621</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1566</v>
-      </c>
-      <c r="J4" t="n">
-        <v>77</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-9.278441</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.647621</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1566</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-9.283511747350881</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.6460277194692</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1133</v>
-      </c>
-      <c r="J5" t="n">
-        <v>73</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-9.28351174735088</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.6460277194692</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>MI PEQUEÑO MUNDO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-9.281269999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.642674</v>
-      </c>
-      <c r="I6" t="n">
-        <v>28</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-9.28127</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.642674</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>86278 MARIO TORRES MEZARINA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-9.357716</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.599959</v>
-      </c>
-      <c r="I7" t="n">
-        <v>252</v>
-      </c>
-      <c r="J7" t="n">
-        <v>21</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-9.357716</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.599959</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>86277 MARIO VAZQUEZ VARELA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-9.328795</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.55286599999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>266</v>
-      </c>
-      <c r="J8" t="n">
-        <v>20</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-9.328795</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.552866</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-9.319845000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.603679</v>
-      </c>
-      <c r="I9" t="n">
-        <v>328</v>
-      </c>
-      <c r="J9" t="n">
-        <v>36</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-9.319845</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.603679</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>86894 FERMIN CARRION MATOS</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-9.358824</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.552072</v>
-      </c>
-      <c r="I10" t="n">
-        <v>242</v>
-      </c>
-      <c r="J10" t="n">
-        <v>19</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-9.358824</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.552072</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>ALFRED NOBEL</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-9.282035</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.64805800000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>492</v>
-      </c>
-      <c r="J11" t="n">
-        <v>35</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-9.282035</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.648058</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>SAN PEDRO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-9.280737</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.64758</v>
-      </c>
-      <c r="I12" t="n">
-        <v>447</v>
-      </c>
-      <c r="J12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-9.280737</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.64758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>JOB MOISES</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-9.28097</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.64514</v>
-      </c>
-      <c r="I13" t="n">
-        <v>175</v>
-      </c>
-      <c r="J13" t="n">
-        <v>16</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-9.28097</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.64514</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>NUESTRA SEÑORA DE LA SABIDURIA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-9.284584000000001</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.642247</v>
-      </c>
-      <c r="I14" t="n">
-        <v>208</v>
-      </c>
-      <c r="J14" t="n">
-        <v>11</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-9.284584</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.642247</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/ANCASH-CARHUAZ-CARHUAZ.xlsx
+++ b/ZonasEscolares/excels/ANCASH-CARHUAZ-CARHUAZ.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>908803</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>NUESTRA SEÑORA DE LA SABIDURIA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-9.27964</t>
+          <t>-9.284584</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.645572</t>
+          <t>-77.642247</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20258</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>86314 DIVINO MAESTRO</t>
+          <t>070</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.284394</t>
+          <t>-9.27964</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.59685</t>
+          <t>-77.645572</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>358</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>824120</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>86269 MARIA AUXILIADORA</t>
+          <t>JOB MOISES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.278441</t>
+          <t>-9.28097</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.647621</t>
+          <t>-77.64514</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20362</t>
+          <t>20951</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>86894 FERMIN CARRION MATOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.28351174735088</t>
+          <t>-9.358824</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.6460277194692</t>
+          <t>-77.552072</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO MUNDO</t>
+          <t>86314 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.28127</t>
+          <t>-9.284394</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.642674</t>
+          <t>-77.59685</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>20772</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>86278 MARIO TORRES MEZARINA</t>
+          <t>86277 MARIO VAZQUEZ VARELA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.357716</t>
+          <t>-9.328795</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.599959</t>
+          <t>-77.552866</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20772</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>86277 MARIO VAZQUEZ VARELA</t>
+          <t>86278 MARIO TORRES MEZARINA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.328795</t>
+          <t>-9.357716</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.552866</t>
+          <t>-77.599959</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20833</t>
+          <t>647981</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.319845</t>
+          <t>-9.280737</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.603679</t>
+          <t>-77.64758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>447</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>86894 FERMIN CARRION MATOS</t>
+          <t>MI PEQUEÑO MUNDO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.358824</t>
+          <t>-9.28127</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.552072</t>
+          <t>-77.642674</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>647981</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.280737</t>
+          <t>-9.319845</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.64758</t>
+          <t>-77.603679</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>824120</t>
+          <t>20362</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JOB MOISES</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.28097</t>
+          <t>-9.28351174735088</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.64514</t>
+          <t>-77.6460277194692</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>908803</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA SABIDURIA</t>
+          <t>86269 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.284584</t>
+          <t>-9.278441</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.642247</t>
+          <t>-77.647621</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/ANCASH-CARHUAZ-CARHUAZ.xlsx
+++ b/ZonasEscolares/excels/ANCASH-CARHUAZ-CARHUAZ.xlsx
@@ -511,22 +511,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>-9.284584</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>-77.642247</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>824120</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>JOB MOISES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.27964</t>
+          <t>175</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.645572</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>-9.28097</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.64514</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>824120</t>
+          <t>647981</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JOB MOISES</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.28097</t>
+          <t>447</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.64514</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>-9.280737</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.64758</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>530373</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>86894 FERMIN CARRION MATOS</t>
+          <t>ALFRED NOBEL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.358824</t>
+          <t>492</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.552072</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-9.282035</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.648058</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20258</t>
+          <t>020951</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>86314 DIVINO MAESTRO</t>
+          <t>86894 FERMIN CARRION MATOS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.284394</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.59685</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-9.358824</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.552072</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20772</t>
+          <t>020833</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>86277 MARIO VAZQUEZ VARELA</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.328795</t>
+          <t>328</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.552866</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-9.319845</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.603679</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>020772</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>86278 MARIO TORRES MEZARINA</t>
+          <t>86277 MARIO VAZQUEZ VARELA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.357716</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.599959</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-9.328795</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.552866</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>647981</t>
+          <t>020606</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>86278 MARIO TORRES MEZARINA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.280737</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.64758</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>-9.357716</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.599959</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>020423</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1007,22 +1007,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>-9.28127</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>-77.642674</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>530373</t>
+          <t>020362</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALFRED NOBEL</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-9.282035</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.648058</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>-9.28351174735088</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-77.6460277194692</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20833</t>
+          <t>020357</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>86269 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.319845</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.603679</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>-9.278441</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.647621</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20362</t>
+          <t>020258</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>86314 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.28351174735088</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.6460277194692</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>-9.284394</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>-77.59685</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>020116</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>86269 MARIA AUXILIADORA</t>
+          <t>070</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.278441</t>
+          <t>358</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.647621</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>-9.27964</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>-77.645572</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">

--- a/ZonasEscolares/excels/ANCASH-CARHUAZ-CARHUAZ.xlsx
+++ b/ZonasEscolares/excels/ANCASH-CARHUAZ-CARHUAZ.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
